--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97717</v>
+        <v>97723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97723</v>
+        <v>97730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97730</v>
+        <v>97734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97734</v>
+        <v>97741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97744</v>
+        <v>97749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97749</v>
+        <v>97757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47709-2025 artfynd.xlsx
+++ b/artfynd/A 47709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74177185</v>
       </c>
       <c r="B2" t="n">
-        <v>97757</v>
+        <v>97767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
